--- a/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
+++ b/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoYK\Documents\GitHub\Engine GenP 3D\LastDance\Assets\Resources\DataBase\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Upgrade Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5E3BA2C-15F5-4824-A95E-695F1C46529F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB397D6-B1C5-4FD2-882E-8FDA926D53F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1164" yWindow="3012" windowWidth="24096" windowHeight="14508" xr2:uid="{0FBE682E-FB0C-4418-8BE2-F8F6B88AE61D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{0FBE682E-FB0C-4418-8BE2-F8F6B88AE61D}"/>
   </bookViews>
   <sheets>
     <sheet name="UpgradeSheet" sheetId="1" r:id="rId1"/>
@@ -39,13 +39,79 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t>Test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OneTwoThree</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxlv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lv1price</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upgradetype</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lv2price</t>
+  </si>
+  <si>
+    <t>lv3price</t>
+  </si>
+  <si>
+    <t>lv4price</t>
+  </si>
+  <si>
+    <t>lv5price</t>
+  </si>
+  <si>
+    <t>lv6price</t>
+  </si>
+  <si>
+    <t>lv7price</t>
+  </si>
+  <si>
+    <t>lv8price</t>
+  </si>
+  <si>
+    <t>lv1value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lv2value</t>
+  </si>
+  <si>
+    <t>lv3value</t>
+  </si>
+  <si>
+    <t>lv4value</t>
+  </si>
+  <si>
+    <t>lv5value</t>
+  </si>
+  <si>
+    <t>lv6value</t>
+  </si>
+  <si>
+    <t>lv7value</t>
+  </si>
+  <si>
+    <t>lv8value</t>
+  </si>
+  <si>
+    <t>lv9price</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lv9value</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -430,23 +496,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4FEBA7-623E-4EAA-9C7F-E935E0D89B65}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:V1"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.58203125" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R1" t="s">
+        <v>18</v>
+      </c>
+      <c r="S1" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
         <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
+++ b/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Upgrade Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB397D6-B1C5-4FD2-882E-8FDA926D53F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D400963-C749-46FF-AABF-D2B6012D9441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{0FBE682E-FB0C-4418-8BE2-F8F6B88AE61D}"/>
   </bookViews>
@@ -57,10 +57,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>lv2price</t>
   </si>
   <si>
@@ -112,6 +108,10 @@
   </si>
   <si>
     <t>lv9value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -512,7 +512,7 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -521,55 +521,55 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>8</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>16</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>9</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>10</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="S1" t="s">
-        <v>11</v>
-      </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
+++ b/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Upgrade Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoYK\Documents\GitHub\Engine GenP 3D\LastDance\Assets\Resources\DataBase\Upgrade Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB397D6-B1C5-4FD2-882E-8FDA926D53F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{0FBE682E-FB0C-4418-8BE2-F8F6B88AE61D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="16224"/>
   </bookViews>
   <sheets>
     <sheet name="UpgradeSheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -57,10 +56,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>lv2price</t>
   </si>
   <si>
@@ -112,13 +107,17 @@
   </si>
   <si>
     <t>lv9value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -495,16 +494,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4FEBA7-623E-4EAA-9C7F-E935E0D89B65}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:V1"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.58203125" customWidth="1"/>
+    <col min="1" max="1" width="6.796875" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" customWidth="1"/>
     <col min="3" max="3" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -512,7 +511,7 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -521,55 +520,55 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>8</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>16</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>9</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>10</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="S1" t="s">
-        <v>11</v>
-      </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
+++ b/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\LastDance\Assets\Resources\DataBase\Upgrade Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoYK\Documents\GitHub\Engine GenP 3D\LastDance\Assets\Resources\DataBase\Upgrade Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D400963-C749-46FF-AABF-D2B6012D9441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{0FBE682E-FB0C-4418-8BE2-F8F6B88AE61D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="16224"/>
   </bookViews>
   <sheets>
     <sheet name="UpgradeSheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -112,13 +111,21 @@
   </si>
   <si>
     <t>value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Percent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테스트 이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -495,16 +502,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4FEBA7-623E-4EAA-9C7F-E935E0D89B65}">
-  <dimension ref="A1:V1"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.58203125" customWidth="1"/>
+    <col min="1" max="1" width="6.796875" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" customWidth="1"/>
     <col min="3" max="3" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -570,6 +577,74 @@
       </c>
       <c r="V1" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>7</v>
+      </c>
+      <c r="N2">
+        <v>8</v>
+      </c>
+      <c r="O2">
+        <v>9</v>
+      </c>
+      <c r="P2">
+        <v>10</v>
+      </c>
+      <c r="Q2">
+        <v>11</v>
+      </c>
+      <c r="R2">
+        <v>12</v>
+      </c>
+      <c r="S2">
+        <v>12</v>
+      </c>
+      <c r="T2">
+        <v>13</v>
+      </c>
+      <c r="U2">
+        <v>13</v>
+      </c>
+      <c r="V2">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
+++ b/Assets/Resources/DataBase/Upgrade Data/UpgradeDB.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -119,6 +119,14 @@
   </si>
   <si>
     <t>테스트 이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Add</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕하세용</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -503,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.796875" customWidth="1"/>
@@ -647,6 +655,74 @@
         <v>15</v>
       </c>
     </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+      <c r="N3">
+        <v>5</v>
+      </c>
+      <c r="O3">
+        <v>6</v>
+      </c>
+      <c r="P3">
+        <v>6</v>
+      </c>
+      <c r="Q3">
+        <v>7</v>
+      </c>
+      <c r="R3">
+        <v>7</v>
+      </c>
+      <c r="S3">
+        <v>8</v>
+      </c>
+      <c r="T3">
+        <v>8</v>
+      </c>
+      <c r="U3">
+        <v>9</v>
+      </c>
+      <c r="V3">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
